--- a/data/trans_dic/P1412-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1412-Habitat-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,37</t>
+          <t>0,15; 1,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,35</t>
+          <t>0,16; 1,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,37</t>
+          <t>0,26; 1,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,75</t>
+          <t>0,3; 1,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,36</t>
+          <t>0,15; 1,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,33</t>
+          <t>0,38; 1,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,18</t>
+          <t>0,31; 1,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,04</t>
+          <t>0,23; 1,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,08</t>
+          <t>0,4; 1,03</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,94</t>
+          <t>0,45; 1,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,74</t>
+          <t>0,49; 1,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,02</t>
+          <t>0,3; 1,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,31</t>
+          <t>0,22; 1,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,04</t>
+          <t>0,1; 0,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,8</t>
+          <t>0,18; 0,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,31</t>
+          <t>0,42; 1,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,11</t>
+          <t>0,35; 1,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,72</t>
+          <t>0,29; 0,8</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,36</t>
+          <t>0,14; 1,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,1</t>
+          <t>0,41; 2,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,43</t>
+          <t>0,58; 2,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,16</t>
+          <t>0,53; 2,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,52</t>
+          <t>0,15; 1,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,69</t>
+          <t>0,16; 0,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,48</t>
+          <t>0,41; 1,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,44</t>
+          <t>0,46; 1,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,24</t>
+          <t>0,43; 1,34</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,29</t>
+          <t>0,21; 1,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,1</t>
+          <t>0,19; 1,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,96</t>
+          <t>0,71; 1,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,04</t>
+          <t>0,1; 0,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,44</t>
+          <t>0,31; 1,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,09</t>
+          <t>0,44; 1,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,84</t>
+          <t>0,21; 0,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,05</t>
+          <t>0,3; 1,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,35</t>
+          <t>0,69; 1,4</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,02</t>
+          <t>0,41; 1,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,1</t>
+          <t>0,5; 1,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,23</t>
+          <t>0,68; 1,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,04</t>
+          <t>0,45; 1,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,85</t>
+          <t>0,31; 0,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,69</t>
+          <t>0,39; 0,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,93</t>
+          <t>0,52; 0,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 0,87</t>
+          <t>0,45; 0,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,85</t>
+          <t>0,59; 0,93</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>4166</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5045</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>9462</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>932; 9626</t>
+          <t>1076; 9863</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1072; 9140</t>
+          <t>1048; 9052</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1690; 8691</t>
+          <t>1820; 8210</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2161; 12225</t>
+          <t>2094; 11975</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1022; 9166</t>
+          <t>1024; 10179</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2767; 8940</t>
+          <t>2805; 9011</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4491; 16582</t>
+          <t>4399; 17001</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3101; 13970</t>
+          <t>3074; 14491</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5647; 14156</t>
+          <t>5737; 14685</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>6388</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9341</t>
+          <t>10488</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4352; 19776</t>
+          <t>4563; 19936</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4742; 17792</t>
+          <t>4968; 18063</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2503; 12146</t>
+          <t>3181; 12115</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2357; 13491</t>
+          <t>2230; 14563</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1015; 10883</t>
+          <t>1015; 9541</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1280; 7641</t>
+          <t>1880; 8602</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9230; 26806</t>
+          <t>8562; 26250</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7712; 22934</t>
+          <t>7163; 22773</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5025; 15562</t>
+          <t>6228; 16940</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8592</t>
+          <t>9593</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11213</t>
+          <t>12836</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1018; 10310</t>
+          <t>1023; 10061</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3765; 15976</t>
+          <t>3085; 16106</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4454; 17019</t>
+          <t>4633; 19125</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4062; 16760</t>
+          <t>4105; 16194</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1267; 11911</t>
+          <t>1170; 10976</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>778; 6427</t>
+          <t>1266; 7754</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6467; 22739</t>
+          <t>6342; 21984</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6420; 22288</t>
+          <t>7161; 23526</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6095; 20199</t>
+          <t>6849; 21517</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11393</t>
+          <t>12524</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7063</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>18456</t>
+          <t>20857</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2023; 12204</t>
+          <t>2012; 12083</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1659; 10283</t>
+          <t>1763; 10133</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6622; 18202</t>
+          <t>6990; 19334</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1083; 10935</t>
+          <t>1075; 9562</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3176; 15033</t>
+          <t>3220; 14852</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3719; 11924</t>
+          <t>4906; 14097</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4119; 16722</t>
+          <t>4173; 17718</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6114; 20740</t>
+          <t>5981; 19853</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12359; 27184</t>
+          <t>14454; 29553</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30153</t>
+          <t>32671</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17930</t>
+          <t>20972</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>48083</t>
+          <t>53643</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14015; 34907</t>
+          <t>14192; 34240</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>16843; 37325</t>
+          <t>16958; 38075</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21197; 42526</t>
+          <t>23976; 45421</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16104; 37053</t>
+          <t>16087; 36747</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10542; 30233</t>
+          <t>11125; 30679</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12410; 25356</t>
+          <t>14728; 28149</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34978; 64582</t>
+          <t>35976; 65540</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>33386; 60484</t>
+          <t>31245; 59836</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>36207; 60708</t>
+          <t>42561; 67365</t>
         </is>
       </c>
     </row>
